--- a/Weekly_paid_payment_Details_September_2026.xlsx
+++ b/Weekly_paid_payment_Details_September_2026.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_September_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD23786F-1B1A-4A77-B706-ECF33B989B38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E528575-1281-49FE-91FB-FF07321625C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{68E78659-9BFD-4944-9A50-DCADFD4AF0BA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{68E78659-9BFD-4944-9A50-DCADFD4AF0BA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Date_05-09-22026 to 11-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Date_19-09-2026 to 25-09-2026" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -63,22 +64,31 @@
     <t>PURCHASE  LIST,WEEKLY PAYMENT</t>
   </si>
   <si>
+    <t xml:space="preserve">Sri Sai Chinthamani Traders- Welding Rods 7018 (Mangalam) 4mm 6 Packets </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 19-09-2026</t>
+  </si>
+  <si>
+    <t>CNT/26-27/26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 09-09-2026</t>
+  </si>
+  <si>
+    <t>CNT/26-27/22</t>
+  </si>
+  <si>
     <t>Sri Sai Chinthamani Traders- L angles &amp; cutting wheels For Lab</t>
   </si>
   <si>
-    <t>CNT/26-27/22</t>
+    <t>10-09-02026</t>
   </si>
   <si>
     <t>CNT/26-27/24</t>
   </si>
   <si>
     <t>Sri Sai Chinthamani Traders- Welding rods 2 packets &amp; Cutting wheels mesurment tape</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 09-09-2026</t>
-  </si>
-  <si>
-    <t>10-09-02026</t>
   </si>
 </sst>
 </file>
@@ -602,13 +612,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
-      </c>
       <c r="D4" s="6" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E4" s="5">
         <v>3193</v>
@@ -620,13 +630,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E5" s="9">
         <v>2040</v>
@@ -657,4 +667,109 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C2977CE-B17F-4151-B580-5E4D458583BB}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4800</v>
+      </c>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="12">
+        <f>SUM(E4:E6)</f>
+        <v>4800</v>
+      </c>
+      <c r="F7" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>